--- a/public/modelos/PCMD-02-Ativos-Criticidade-Exemplo.xlsx
+++ b/public/modelos/PCMD-02-Ativos-Criticidade-Exemplo.xlsx
@@ -682,7 +682,7 @@
       <row>0</row>
       <rowOff>209550</rowOff>
     </from>
-    <ext cx="1762125" cy="409575"/>
+    <ext cx="1415105" cy="409575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -712,7 +712,7 @@
       <row>0</row>
       <rowOff>228600</rowOff>
     </from>
-    <ext cx="1647825" cy="381000"/>
+    <ext cx="1316376" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -742,7 +742,7 @@
       <row>0</row>
       <rowOff>247650</rowOff>
     </from>
-    <ext cx="1495425" cy="342900"/>
+    <ext cx="1184739" cy="342900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -772,7 +772,7 @@
       <row>0</row>
       <rowOff>142875</rowOff>
     </from>
-    <ext cx="2362200" cy="542925"/>
+    <ext cx="1875836" cy="542925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -802,7 +802,7 @@
       <row>0</row>
       <rowOff>142875</rowOff>
     </from>
-    <ext cx="2381250" cy="552450"/>
+    <ext cx="1908746" cy="552450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
